--- a/docs/demo/BIS-Prioritisation-Demo-Bridges.xlsx
+++ b/docs/demo/BIS-Prioritisation-Demo-Bridges.xlsx
@@ -2118,12 +2118,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Transport for NSW</t>
+          <t>State Roads Authority</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>TfNSW</t>
+          <t>condition band</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Transport for NSW</t>
+          <t>State Roads Authority</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>TfNSW</t>
+          <t>condition band</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Transport for NSW</t>
+          <t>State Roads Authority</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>TfNSW</t>
+          <t>condition band</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Transport for NSW</t>
+          <t>State Roads Authority</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>TfNSW</t>
+          <t>condition band</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Transport for NSW</t>
+          <t>State Roads Authority</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>TfNSW</t>
+          <t>condition band</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
